--- a/data/trans_camb/P1413-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P1413-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,58</t>
+          <t>0,84</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,39</t>
+          <t>10,69</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5,1</t>
+          <t>5,38</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,49; -2,83</t>
+          <t>-10,71; -2,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,41; -1,83</t>
+          <t>-10,29; -1,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 5,5</t>
+          <t>-3,53; 5,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 5,12</t>
+          <t>-5,55; 5,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,02; -0,39</t>
+          <t>-10,01; -0,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,7; 15,2</t>
+          <t>5,42; 15,48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-7,22; -0,97</t>
+          <t>-7,65; -1,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-8,85; -2,73</t>
+          <t>-8,76; -2,41</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,67; 8,25</t>
+          <t>1,98; 8,6</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>83,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>39,62%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-67,19; -23,65</t>
+          <t>-67,08; -22,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-62,82; -13,21</t>
+          <t>-63,12; -13,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-21,48; 48,84</t>
+          <t>-21,7; 50,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-39,91; 51,98</t>
+          <t>-38,08; 49,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-64,89; -3,38</t>
+          <t>-64,07; -1,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,52; 153,51</t>
+          <t>33,92; 158,31</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-48,36; -6,7</t>
+          <t>-50,28; -8,74</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-58,23; -22,25</t>
+          <t>-57,33; -19,33</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,01; 71,47</t>
+          <t>12,35; 72,85</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6,93</t>
+          <t>6,59</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,3</t>
+          <t>11,11</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>8,16</t>
+          <t>8,46</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 2,57</t>
+          <t>-5,86; 2,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,25; -0,08</t>
+          <t>-8,29; -0,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,4; 11,37</t>
+          <t>1,58; 11,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,97; 2,74</t>
+          <t>-8,02; 2,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,39; -0,46</t>
+          <t>-10,46; -0,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,32; 15,62</t>
+          <t>5,98; 16,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,79; 1,13</t>
+          <t>-5,72; 0,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,05; -1,62</t>
+          <t>-8,16; -1,58</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,33; 11,38</t>
+          <t>5,06; 12,35</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>65,49%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>60,95%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>62,62%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-49,15; 32,08</t>
+          <t>-48,64; 36,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-69,33; 1,02</t>
+          <t>-66,38; -0,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17,91; 144,96</t>
+          <t>13,02; 143,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-41,97; 18,36</t>
+          <t>-41,61; 20,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-53,77; -2,71</t>
+          <t>-51,25; 3,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,42; 115,16</t>
+          <t>29,48; 119,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-37,8; 10,19</t>
+          <t>-37,74; 7,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-52,53; -13,81</t>
+          <t>-53,25; -13,17</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>28,32; 97,04</t>
+          <t>32,08; 109,67</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-4,64</t>
+          <t>3,28</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,78</t>
+          <t>15,21</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,64</t>
+          <t>6,8</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-12,64; -4,16</t>
+          <t>-12,48; -4,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-14,76; -6,65</t>
+          <t>-14,69; -6,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-14,3; 5,26</t>
+          <t>-1,89; 8,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-14,25; 1,62</t>
+          <t>-13,67; 2,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,93; 8,94</t>
+          <t>-9,33; 8,87</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,45; 23,56</t>
+          <t>6,33; 23,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-11,35; -3,89</t>
+          <t>-11,32; -3,7</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-11,91; -4,58</t>
+          <t>-12,03; -4,43</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-12,35; 8,15</t>
+          <t>2,48; 10,69</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-24,97%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>72,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-3,35%</t>
+          <t>35,5%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-59,88; -25,41</t>
+          <t>-59,5; -24,32</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-70,24; -39,02</t>
+          <t>-71,15; -39,27</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-71,52; 29,99</t>
+          <t>-8,78; 50,82</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-53,55; 11,44</t>
+          <t>-52,95; 12,74</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-35,08; 56,38</t>
+          <t>-36,36; 53,95</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>23,95; 148,04</t>
+          <t>23,31; 144,71</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-52,97; -22,16</t>
+          <t>-52,86; -21,87</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-57,17; -26,25</t>
+          <t>-57,09; -25,33</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-58,18; 43,98</t>
+          <t>11,47; 62,77</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,13</t>
+          <t>0,62</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,94</t>
+          <t>8,01</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>11,6</t>
+          <t>3,74</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-12,28; -6,3</t>
+          <t>-12,2; -6,54</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-14,18; -8,41</t>
+          <t>-14,18; -8,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 4,8</t>
+          <t>-2,88; 3,82</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,93; 1,3</t>
+          <t>-7,03; 1,08</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,93; -2,46</t>
+          <t>-9,98; -2,58</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,45; 46,89</t>
+          <t>4,07; 12,08</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-9,14; -4,49</t>
+          <t>-9,42; -4,46</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-11,4; -6,89</t>
+          <t>-11,75; -6,96</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,06; 34,8</t>
+          <t>1,11; 6,1</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>119,4%</t>
+          <t>41,69%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>58,08%</t>
+          <t>18,72%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-56,39; -32,85</t>
+          <t>-55,77; -34,15</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-64,56; -44,42</t>
+          <t>-63,76; -44,55</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-8,68; 25,57</t>
+          <t>-13,12; 20,07</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-33,19; 7,37</t>
+          <t>-32,73; 6,34</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-47,05; -14,55</t>
+          <t>-46,76; -15,39</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>32,29; 277,88</t>
+          <t>17,86; 69,68</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-43,57; -23,87</t>
+          <t>-44,38; -23,93</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-53,61; -36,21</t>
+          <t>-54,46; -36,24</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>15,13; 180,68</t>
+          <t>4,63; 32,5</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2,94</t>
+          <t>1,85</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,52</t>
+          <t>18,21</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>10,39</t>
+          <t>11,51</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-15,28; -5,66</t>
+          <t>-15,13; -5,62</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-11,91; -2,22</t>
+          <t>-12,18; -2,41</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 8,61</t>
+          <t>-3,47; 6,94</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 6,5</t>
+          <t>-3,08; 6,19</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 0,38</t>
+          <t>-8,83; 0,15</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,0; 20,98</t>
+          <t>13,85; 22,77</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-7,01; 0,12</t>
+          <t>-7,38; -0,02</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-9,33; -2,4</t>
+          <t>-8,94; -2,72</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4,1; 14,68</t>
+          <t>7,82; 15,09</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>67,48%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>55,93%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-69,16; -33,68</t>
+          <t>-68,52; -35,03</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-54,2; -14,44</t>
+          <t>-53,94; -14,47</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-12,29; 55,58</t>
+          <t>-16,32; 43,31</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-12,92; 34,84</t>
+          <t>-13,42; 31,7</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-35,89; 2,3</t>
+          <t>-36,32; 0,86</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,38; 109,21</t>
+          <t>55,73; 122,36</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-30,77; 0,68</t>
+          <t>-32,21; -0,1</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-40,81; -12,9</t>
+          <t>-39,35; -14,13</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>19,39; 78,53</t>
+          <t>35,15; 82,09</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6,88</t>
+          <t>6,78</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,96</t>
+          <t>9,79</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>8,35</t>
+          <t>8,64</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 3,44</t>
+          <t>-1,64; 3,49</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 0,01</t>
+          <t>-3,65; -0,13</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1,76; 14,61</t>
+          <t>2,27; 13,89</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 2,3</t>
+          <t>-4,09; 2,46</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-9,58; -3,32</t>
+          <t>-9,5; -3,38</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,36; 13,76</t>
+          <t>6,24; 13,23</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 2,16</t>
+          <t>-3,27; 1,98</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-8,45; -3,19</t>
+          <t>-8,22; -3,03</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>5,14; 11,62</t>
+          <t>5,57; 11,78</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>362,64%</t>
+          <t>357,7%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>51,59%</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-73,4; 425,31</t>
+          <t>-67,78; 402,11</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1873,37 +1873,37 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>30,49; 1356,06</t>
+          <t>53,03; 1295,42</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-18,66; 12,19</t>
+          <t>-18,54; 12,73</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-44,3; -17,68</t>
+          <t>-43,29; -17,68</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>28,88; 73,71</t>
+          <t>29,32; 71,86</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-19,45; 13,18</t>
+          <t>-18,47; 13,12</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-46,21; -20,31</t>
+          <t>-46,13; -18,98</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>28,4; 74,55</t>
+          <t>30,31; 74,85</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1,36</t>
+          <t>2,48</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>14,71</t>
+          <t>11,55</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>8,25</t>
+          <t>7,16</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-8,75; -5,52</t>
+          <t>-8,86; -5,63</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-9,63; -6,34</t>
+          <t>-9,61; -6,34</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 3,57</t>
+          <t>0,56; 4,33</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 0,7</t>
+          <t>-3,0; 0,7</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-7,39; -3,68</t>
+          <t>-7,14; -3,67</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,88; 27,59</t>
+          <t>9,69; 13,32</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-5,37; -2,89</t>
+          <t>-5,33; -2,89</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-7,96; -5,44</t>
+          <t>-7,84; -5,51</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>4,83; 15,18</t>
+          <t>5,87; 8,43</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>76,44%</t>
+          <t>59,99%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>40,35%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-51,44; -35,88</t>
+          <t>-51,76; -36,36</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-56,14; -40,99</t>
+          <t>-56,02; -41,84</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-13,54; 23,05</t>
+          <t>3,17; 28,22</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-14,12; 3,88</t>
+          <t>-14,74; 4,0</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-36,33; -20,08</t>
+          <t>-35,57; -19,75</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>50,3; 145,55</t>
+          <t>47,31; 73,08</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-29,12; -16,76</t>
+          <t>-28,89; -16,84</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-43,53; -31,75</t>
+          <t>-42,65; -31,94</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>26,98; 85,72</t>
+          <t>31,84; 49,92</t>
         </is>
       </c>
     </row>
